--- a/data/box_data.xlsx
+++ b/data/box_data.xlsx
@@ -1,27 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QKO-2201-19\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7CDEF9-2687-406F-9249-DEB83DF624B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98E9D6D0-138F-4971-9D82-59BE114E22CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pack_boxes" sheetId="1" r:id="rId1"/>
     <sheet name="product_boxes" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">product_boxes!$A$1:$H$93</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="201">
   <si>
     <t>name</t>
   </si>
@@ -93,15 +109,6 @@
   </si>
   <si>
     <t>본사-QTEX</t>
-  </si>
-  <si>
-    <t>본사-장방형</t>
-  </si>
-  <si>
-    <t>본사-1500 장방형</t>
-  </si>
-  <si>
-    <t>본사-QLV</t>
   </si>
   <si>
     <t>QCML1500제품박스</t>
@@ -619,9 +626,6 @@
   </si>
   <si>
     <t>중계-#5 타워</t>
-  </si>
-  <si>
-    <t>중계-#6 TOGU전용</t>
   </si>
   <si>
     <t>중계-#7</t>
@@ -647,9 +651,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="180" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="182" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="183" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="178" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -757,36 +761,35 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="183" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="16">
     <cellStyle name="常规 2" xfId="2" xr:uid="{8D96EF87-7DEC-4760-B9AC-57429344B315}"/>
@@ -1104,14 +1107,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I29"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="25.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.59765625" customWidth="1"/>
-    <col min="12" max="12" width="26.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.625" customWidth="1"/>
+    <col min="12" max="12" width="26.875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1175,15 +1178,15 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B17" si="1">E3-5</f>
+        <f t="shared" ref="B3:B13" si="1">E3-5</f>
         <v>765</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C17" si="2">F3-5</f>
+        <f t="shared" ref="C3:C14" si="2">F3-5</f>
         <v>375</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D17" si="3">G3-5</f>
+        <f t="shared" ref="D3:D14" si="3">G3-5</f>
         <v>295</v>
       </c>
       <c r="E3">
@@ -1458,80 +1461,80 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>190</v>
       </c>
       <c r="B14">
-        <f t="shared" si="1"/>
-        <v>1245</v>
+        <f>E14-5</f>
+        <v>578</v>
       </c>
       <c r="C14">
         <f t="shared" si="2"/>
-        <v>385</v>
+        <v>346</v>
       </c>
       <c r="D14">
         <f t="shared" si="3"/>
-        <v>245</v>
+        <v>367</v>
       </c>
       <c r="E14">
-        <v>1250</v>
+        <v>583</v>
       </c>
       <c r="F14">
-        <v>390</v>
+        <v>351</v>
       </c>
       <c r="G14">
-        <v>250</v>
+        <v>372</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>191</v>
       </c>
       <c r="B15">
-        <f t="shared" si="1"/>
-        <v>1495</v>
+        <f t="shared" ref="B15:B24" si="4">E15-5</f>
+        <v>485</v>
       </c>
       <c r="C15">
-        <f t="shared" si="2"/>
-        <v>385</v>
+        <f t="shared" ref="C15:C24" si="5">F15-5</f>
+        <v>395</v>
       </c>
       <c r="D15">
-        <f t="shared" si="3"/>
-        <v>245</v>
+        <f t="shared" ref="D15:D24" si="6">G15-5</f>
+        <v>405</v>
       </c>
       <c r="E15">
-        <v>1500</v>
+        <v>490</v>
       </c>
       <c r="F15">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="G15">
-        <v>250</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="B16">
-        <f t="shared" si="1"/>
-        <v>1370</v>
+        <f t="shared" si="4"/>
+        <v>295</v>
       </c>
       <c r="C16">
-        <f t="shared" si="2"/>
-        <v>415</v>
+        <f t="shared" si="5"/>
+        <v>190</v>
       </c>
       <c r="D16">
-        <f t="shared" si="3"/>
-        <v>215</v>
+        <f t="shared" si="6"/>
+        <v>265</v>
       </c>
       <c r="E16">
-        <v>1375</v>
+        <v>300</v>
       </c>
       <c r="F16">
-        <v>420</v>
+        <v>195</v>
       </c>
       <c r="G16">
-        <v>220</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1539,25 +1542,25 @@
         <v>193</v>
       </c>
       <c r="B17">
-        <f>E17-5</f>
-        <v>578</v>
+        <f t="shared" si="4"/>
+        <v>395</v>
       </c>
       <c r="C17">
-        <f t="shared" si="2"/>
-        <v>346</v>
+        <f t="shared" si="5"/>
+        <v>235</v>
       </c>
       <c r="D17">
-        <f t="shared" si="3"/>
-        <v>367</v>
-      </c>
-      <c r="E17" s="2">
-        <v>583</v>
-      </c>
-      <c r="F17" s="2">
-        <v>351</v>
-      </c>
-      <c r="G17" s="2">
-        <v>372</v>
+        <f t="shared" si="6"/>
+        <v>365</v>
+      </c>
+      <c r="E17">
+        <v>400</v>
+      </c>
+      <c r="F17">
+        <v>240</v>
+      </c>
+      <c r="G17">
+        <v>370</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1565,25 +1568,25 @@
         <v>194</v>
       </c>
       <c r="B18">
-        <f t="shared" ref="B18:B29" si="4">E18-5</f>
-        <v>485</v>
+        <f t="shared" si="4"/>
+        <v>925</v>
       </c>
       <c r="C18">
-        <f t="shared" ref="C18:C29" si="5">F18-5</f>
-        <v>395</v>
+        <f t="shared" si="5"/>
+        <v>330</v>
       </c>
       <c r="D18">
-        <f t="shared" ref="D18:D29" si="6">G18-5</f>
-        <v>405</v>
-      </c>
-      <c r="E18" s="2">
-        <v>490</v>
-      </c>
-      <c r="F18" s="2">
-        <v>400</v>
-      </c>
-      <c r="G18" s="2">
-        <v>410</v>
+        <f t="shared" si="6"/>
+        <v>415</v>
+      </c>
+      <c r="E18">
+        <v>930</v>
+      </c>
+      <c r="F18">
+        <v>335</v>
+      </c>
+      <c r="G18">
+        <v>420</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1592,24 +1595,24 @@
       </c>
       <c r="B19">
         <f t="shared" si="4"/>
-        <v>295</v>
+        <v>240</v>
       </c>
       <c r="C19">
         <f t="shared" si="5"/>
-        <v>190</v>
+        <v>245</v>
       </c>
       <c r="D19">
         <f t="shared" si="6"/>
-        <v>265</v>
-      </c>
-      <c r="E19" s="2">
-        <v>300</v>
-      </c>
-      <c r="F19" s="2">
+        <v>190</v>
+      </c>
+      <c r="E19">
+        <v>245</v>
+      </c>
+      <c r="F19">
+        <v>250</v>
+      </c>
+      <c r="G19">
         <v>195</v>
-      </c>
-      <c r="G19" s="2">
-        <v>270</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1618,24 +1621,24 @@
       </c>
       <c r="B20">
         <f t="shared" si="4"/>
-        <v>395</v>
+        <v>1015</v>
       </c>
       <c r="C20">
         <f t="shared" si="5"/>
-        <v>235</v>
+        <v>405</v>
       </c>
       <c r="D20">
         <f t="shared" si="6"/>
-        <v>365</v>
-      </c>
-      <c r="E20" s="2">
-        <v>400</v>
-      </c>
-      <c r="F20" s="2">
-        <v>240</v>
-      </c>
-      <c r="G20" s="2">
-        <v>370</v>
+        <v>270</v>
+      </c>
+      <c r="E20">
+        <v>1020</v>
+      </c>
+      <c r="F20">
+        <v>410</v>
+      </c>
+      <c r="G20">
+        <v>275</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1644,24 +1647,24 @@
       </c>
       <c r="B21">
         <f t="shared" si="4"/>
-        <v>925</v>
+        <v>620</v>
       </c>
       <c r="C21">
         <f t="shared" si="5"/>
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="D21">
         <f t="shared" si="6"/>
-        <v>415</v>
-      </c>
-      <c r="E21" s="2">
-        <v>930</v>
-      </c>
-      <c r="F21" s="2">
-        <v>335</v>
-      </c>
-      <c r="G21" s="2">
-        <v>420</v>
+        <v>395</v>
+      </c>
+      <c r="E21">
+        <v>625</v>
+      </c>
+      <c r="F21">
+        <v>300</v>
+      </c>
+      <c r="G21">
+        <v>400</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1670,24 +1673,24 @@
       </c>
       <c r="B22">
         <f t="shared" si="4"/>
-        <v>790</v>
+        <v>585</v>
       </c>
       <c r="C22">
         <f t="shared" si="5"/>
-        <v>425</v>
+        <v>375</v>
       </c>
       <c r="D22">
         <f t="shared" si="6"/>
-        <v>165</v>
-      </c>
-      <c r="E22" s="2">
-        <v>795</v>
-      </c>
-      <c r="F22" s="2">
-        <v>430</v>
-      </c>
-      <c r="G22" s="2">
-        <v>170</v>
+        <v>445</v>
+      </c>
+      <c r="E22">
+        <v>590</v>
+      </c>
+      <c r="F22">
+        <v>380</v>
+      </c>
+      <c r="G22">
+        <v>450</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1696,24 +1699,24 @@
       </c>
       <c r="B23">
         <f t="shared" si="4"/>
-        <v>240</v>
+        <v>605</v>
       </c>
       <c r="C23">
         <f t="shared" si="5"/>
-        <v>245</v>
+        <v>585</v>
       </c>
       <c r="D23">
         <f t="shared" si="6"/>
-        <v>190</v>
-      </c>
-      <c r="E23" s="2">
-        <v>245</v>
-      </c>
-      <c r="F23" s="2">
-        <v>250</v>
-      </c>
-      <c r="G23" s="2">
-        <v>195</v>
+        <v>305</v>
+      </c>
+      <c r="E23">
+        <v>610</v>
+      </c>
+      <c r="F23">
+        <v>590</v>
+      </c>
+      <c r="G23">
+        <v>310</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1722,133 +1725,29 @@
       </c>
       <c r="B24">
         <f t="shared" si="4"/>
-        <v>1015</v>
+        <v>660</v>
       </c>
       <c r="C24">
         <f t="shared" si="5"/>
-        <v>405</v>
+        <v>500</v>
       </c>
       <c r="D24">
         <f t="shared" si="6"/>
-        <v>270</v>
-      </c>
-      <c r="E24" s="2">
-        <v>1020</v>
-      </c>
-      <c r="F24" s="2">
-        <v>410</v>
-      </c>
-      <c r="G24" s="2">
-        <v>275</v>
+        <v>485</v>
+      </c>
+      <c r="E24">
+        <v>665</v>
+      </c>
+      <c r="F24">
+        <v>505</v>
+      </c>
+      <c r="G24">
+        <v>490</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" t="s">
-        <v>201</v>
-      </c>
-      <c r="B25">
-        <f t="shared" si="4"/>
-        <v>620</v>
-      </c>
-      <c r="C25">
-        <f t="shared" si="5"/>
-        <v>295</v>
-      </c>
-      <c r="D25">
-        <f t="shared" si="6"/>
-        <v>395</v>
-      </c>
-      <c r="E25" s="2">
-        <v>625</v>
-      </c>
-      <c r="F25" s="2">
-        <v>300</v>
-      </c>
-      <c r="G25" s="2">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" t="s">
-        <v>202</v>
-      </c>
-      <c r="B26">
-        <f t="shared" si="4"/>
-        <v>585</v>
-      </c>
-      <c r="C26">
-        <f t="shared" si="5"/>
-        <v>375</v>
-      </c>
-      <c r="D26">
-        <f t="shared" si="6"/>
-        <v>445</v>
-      </c>
-      <c r="E26" s="2">
-        <v>590</v>
-      </c>
-      <c r="F26" s="2">
-        <v>380</v>
-      </c>
-      <c r="G26">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" t="s">
-        <v>203</v>
-      </c>
-      <c r="B27">
-        <f t="shared" si="4"/>
-        <v>605</v>
-      </c>
-      <c r="C27">
-        <f t="shared" si="5"/>
-        <v>585</v>
-      </c>
-      <c r="D27">
-        <f t="shared" si="6"/>
-        <v>305</v>
-      </c>
-      <c r="E27" s="2">
-        <v>610</v>
-      </c>
-      <c r="F27" s="2">
-        <v>590</v>
-      </c>
-      <c r="G27" s="2">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" t="s">
-        <v>204</v>
-      </c>
-      <c r="B28">
-        <f t="shared" si="4"/>
-        <v>660</v>
-      </c>
-      <c r="C28">
-        <f t="shared" si="5"/>
-        <v>500</v>
-      </c>
-      <c r="D28">
-        <f t="shared" si="6"/>
-        <v>485</v>
-      </c>
-      <c r="E28" s="2">
-        <v>665</v>
-      </c>
-      <c r="F28" s="2">
-        <v>505</v>
-      </c>
-      <c r="G28" s="2">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" t="str">
-        <f t="shared" ref="A18:A29" si="7">I29&amp;J29</f>
+      <c r="A25" t="str">
+        <f t="shared" ref="A25" si="7">I25&amp;J25</f>
         <v/>
       </c>
     </row>
@@ -1861,10 +1760,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H93"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="16.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1875,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -1895,10 +1794,10 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C2">
         <v>60</v>
@@ -1918,10 +1817,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>60</v>
@@ -1941,10 +1840,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>460</v>
@@ -1962,15 +1861,15 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>1250</v>
@@ -1990,10 +1889,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>660</v>
@@ -2013,10 +1912,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>107</v>
@@ -2036,10 +1935,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>135</v>
@@ -2059,10 +1958,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>95</v>
@@ -2082,10 +1981,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>130</v>
@@ -2105,10 +2004,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>60</v>
@@ -2128,10 +2027,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C12">
         <v>60</v>
@@ -2151,10 +2050,10 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>60</v>
@@ -2174,10 +2073,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>60</v>
@@ -2197,10 +2096,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>501</v>
@@ -2220,10 +2119,10 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <v>78</v>
@@ -2243,10 +2142,10 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>78</v>
@@ -2266,10 +2165,10 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>78</v>
@@ -2289,10 +2188,10 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C19">
         <v>78</v>
@@ -2312,10 +2211,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C20">
         <v>78</v>
@@ -2335,10 +2234,10 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C21">
         <v>78</v>
@@ -2358,10 +2257,10 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C22">
         <v>78</v>
@@ -2381,10 +2280,10 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C23">
         <v>880</v>
@@ -2404,10 +2303,10 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C24">
         <v>1010</v>
@@ -2427,10 +2326,10 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C25">
         <v>260</v>
@@ -2450,10 +2349,10 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C26">
         <v>142</v>
@@ -2473,10 +2372,10 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C27">
         <v>220</v>
@@ -2494,15 +2393,15 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C28">
         <v>59</v>
@@ -2522,10 +2421,10 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C29">
         <v>59</v>
@@ -2545,10 +2444,10 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C30">
         <v>48</v>
@@ -2568,10 +2467,10 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C31">
         <v>240</v>
@@ -2591,10 +2490,10 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C32">
         <v>240</v>
@@ -2614,10 +2513,10 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C33">
         <v>300</v>
@@ -2637,10 +2536,10 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B34" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C34">
         <v>300</v>
@@ -2660,10 +2559,10 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C35">
         <v>350</v>
@@ -2683,10 +2582,10 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C36">
         <v>380</v>
@@ -2706,10 +2605,10 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C37">
         <v>380</v>
@@ -2729,10 +2628,10 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C38">
         <v>258</v>
@@ -2752,10 +2651,10 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C39">
         <v>340</v>
@@ -2775,10 +2674,10 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C40">
         <v>300</v>
@@ -2798,10 +2697,10 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C41">
         <v>107</v>
@@ -2821,10 +2720,10 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C42">
         <v>120</v>
@@ -2844,10 +2743,10 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C43">
         <v>120</v>
@@ -2867,10 +2766,10 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C44">
         <v>178</v>
@@ -2890,10 +2789,10 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B45" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C45">
         <v>130</v>
@@ -2913,10 +2812,10 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B46" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C46">
         <v>135</v>
@@ -2936,10 +2835,10 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C47">
         <v>135</v>
@@ -2959,10 +2858,10 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B48" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C48">
         <v>170</v>
@@ -2982,10 +2881,10 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B49" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C49">
         <v>170</v>
@@ -3005,10 +2904,10 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B50" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C50">
         <v>95</v>
@@ -3028,10 +2927,10 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B51" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C51">
         <v>95</v>
@@ -3051,10 +2950,10 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B52" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C52">
         <v>460</v>
@@ -3072,15 +2971,15 @@
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C53">
         <v>465</v>
@@ -3098,15 +2997,15 @@
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B54" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C54">
         <v>360</v>
@@ -3124,15 +3023,15 @@
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B55" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C55">
         <v>300</v>
@@ -3150,15 +3049,15 @@
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B56" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C56">
         <v>300</v>
@@ -3176,15 +3075,15 @@
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C57">
         <v>110</v>
@@ -3204,10 +3103,10 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B58" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C58">
         <v>110</v>
@@ -3227,10 +3126,10 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C59">
         <v>110</v>
@@ -3250,10 +3149,10 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C60">
         <v>78</v>
@@ -3273,10 +3172,10 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B61" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C61">
         <v>78</v>
@@ -3296,10 +3195,10 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B62" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C62">
         <v>78</v>
@@ -3319,10 +3218,10 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B63" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C63">
         <v>78</v>
@@ -3342,10 +3241,10 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B64" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C64">
         <v>78</v>
@@ -3365,10 +3264,10 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C65">
         <v>78</v>
@@ -3388,10 +3287,10 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C66">
         <v>78</v>
@@ -3411,10 +3310,10 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C67">
         <v>78</v>
@@ -3434,10 +3333,10 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B68" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C68">
         <v>95</v>
@@ -3457,10 +3356,10 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B69" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C69">
         <v>95</v>
@@ -3480,10 +3379,10 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B70" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C70">
         <v>95</v>
@@ -3503,10 +3402,10 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C71">
         <v>95</v>
@@ -3526,10 +3425,10 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B72" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C72">
         <v>95</v>
@@ -3549,10 +3448,10 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B73" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C73">
         <v>95</v>
@@ -3572,10 +3471,10 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B74" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C74">
         <v>93</v>
@@ -3595,10 +3494,10 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B75" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C75">
         <v>95</v>
@@ -3618,10 +3517,10 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B76" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C76">
         <v>95</v>
@@ -3641,10 +3540,10 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B77" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C77">
         <v>55</v>
@@ -3664,10 +3563,10 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C78">
         <v>55</v>
@@ -3687,10 +3586,10 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B79" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C79">
         <v>55</v>
@@ -3710,10 +3609,10 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B80" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C80">
         <v>55</v>
@@ -3733,10 +3632,10 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B81" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C81">
         <v>55</v>
@@ -3756,10 +3655,10 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B82" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C82">
         <v>55</v>
@@ -3779,10 +3678,10 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B83" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C83">
         <v>55</v>
@@ -3802,10 +3701,10 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B84" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C84">
         <v>78</v>
@@ -3825,10 +3724,10 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B85" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C85">
         <v>78</v>
@@ -3848,10 +3747,10 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B86" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C86">
         <v>130</v>
@@ -3871,10 +3770,10 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B87" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C87">
         <v>128</v>
@@ -3894,10 +3793,10 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B88" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C88">
         <v>128</v>
@@ -3917,10 +3816,10 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C89">
         <v>128</v>
@@ -3940,10 +3839,10 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B90" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C90">
         <v>128</v>
@@ -3963,10 +3862,10 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B91" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C91">
         <v>78</v>
@@ -3986,10 +3885,10 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B92" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C92">
         <v>1250</v>
@@ -4009,10 +3908,10 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B93" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C93">
         <v>1500</v>
@@ -4031,6 +3930,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H93" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
